--- a/artfynd/A 42636-2025 artfynd.xlsx
+++ b/artfynd/A 42636-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111286485</v>
+        <v>111929377</v>
       </c>
       <c r="B2" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>85534</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,48 +686,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>241</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gransotdyna</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Camarops tubulina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Shear</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bornsviken, Ramsbergs sn, Vstm</t>
+          <t>Bornsviken, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>523178.935673703</v>
+        <v>523350</v>
       </c>
       <c r="R2" t="n">
-        <v>6619622.816676911</v>
+        <v>6619533</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-08-03</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-08-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112299899</v>
+        <v>112792310</v>
       </c>
       <c r="B3" t="n">
-        <v>90878</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -815,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -842,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523280</v>
+        <v>523269</v>
       </c>
       <c r="R3" t="n">
-        <v>6619633</v>
+        <v>6619543</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -872,12 +844,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2023-10-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2023-10-15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,65 +877,59 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112280469</v>
+        <v>111286485</v>
       </c>
       <c r="B4" t="n">
-        <v>95748</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bornsviken, Vstm</t>
+          <t>Bornsviken, Ramsbergs sn, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523208</v>
+        <v>523179</v>
       </c>
       <c r="R4" t="n">
-        <v>6619697</v>
+        <v>6619623</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,12 +953,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2023-08-03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2023-08-03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,6 +983,1598 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>112792307</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bornsviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>523248</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6619553</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>119371856</v>
+      </c>
+      <c r="B6" t="n">
+        <v>93216</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1440</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Brödtaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hydnellum versipelle</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bornsviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>523350</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6619533</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>112792282</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92097</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1588</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Violmussling</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Trichaptum laricinum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bornsviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>523248</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6619573</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>111286975</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bornsviken, Ramsbergs sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>523268</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6619560</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-08-03</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-08-03</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>111350581</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bornsviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>523217</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6619742</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-08-03</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-08-03</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>111350605</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bornsviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>523233</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6619467</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-08-03</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-08-03</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>112792301</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bornsviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>523244</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6619565</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>112280507</v>
+      </c>
+      <c r="B12" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bornsviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>523280</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6619633</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-09-23</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-09-23</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>112280522</v>
+      </c>
+      <c r="B13" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bornsviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>523323</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6619602</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-09-23</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-09-23</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>112792267</v>
+      </c>
+      <c r="B14" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bornsviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>523279</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6619603</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>112792277</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bornsviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>523261</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6619591</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>112792280</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Bornsviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>523232</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6619597</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>112792313</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Bornsviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>523264</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6619537</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>119371589</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Bornsviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>523305</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6619720</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-04-30</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-04-30</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>112280469</v>
+      </c>
+      <c r="B19" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Bornsviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>523208</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6619697</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2023-09-23</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2023-09-23</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42636-2025 artfynd.xlsx
+++ b/artfynd/A 42636-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111929377</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112792310</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111286485</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1084,6 +1104,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112792307</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1205,6 +1230,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119371856</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1306,6 +1336,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112792282</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1415,6 +1450,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111286975</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1524,6 +1564,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111350581</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1633,6 +1678,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111350605</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1734,6 +1784,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112792301</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1835,6 +1890,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112280507</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1936,6 +1996,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112280522</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2045,6 +2110,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112792267</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2146,6 +2216,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112792277</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2247,6 +2322,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112792280</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2348,6 +2428,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112792313</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2465,6 +2550,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119371589</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2575,8 +2665,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112280469</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>